--- a/Result/checksun_type/鋁合金鋼圈.xlsx
+++ b/Result/checksun_type/鋁合金鋼圈.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>15.97</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>16.22</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>16.67</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>16.22</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>16.67</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>179.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>442.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>442.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>391.2</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>1019.6</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>1019.6</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-0.2691451814905577</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>179</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>179.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>15.97</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>16.24</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>16.7</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>16.24</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>16.7</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>737.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>569.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>569.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>418.6</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>1019.62</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>1019.62</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>24.29779375436681</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>737</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>737.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>15.96</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>16.26</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>16.74</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>16.74</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>193.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>444.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>444.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>390.5</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>1007.38</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>1007.38</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-1.260071828492869</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>193</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>193.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>15.97</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>16.29</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>16.78</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>16.29</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>16.78</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>560.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>504.2</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>504.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>404.1</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>1013.26</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>1013.26</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>20.5594084755823</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>560</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>560.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>16.01</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>16.32</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>16.82</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>16.32</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>16.82</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>543.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>427.8</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>427.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>365.0</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>1003.68</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>1003.68</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>11.67440146441896</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>543</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>543.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>16.05</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>16.35</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>16.87</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>16.35</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>16.87</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>816.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>340.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>340</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>359.7</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>1006.68</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>1006.68</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>0.3860199675992249</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>816</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>816.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>16.08</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>16.38</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>16.91</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>16.38</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>16.91</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>112.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>267.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>267.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>295.0</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>1002.68</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>1002.68</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-45.00402574098604</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>112</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>16.14</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>16.42</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>16.95</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>16.42</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>16.95</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>490.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>336.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>336.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>329.5</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>1002.96</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>1002.96</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-32.81109011964406</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>490</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>490.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>16.22</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>16.45</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>16.99</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>16.45</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>16.99</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>178.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>304.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>304</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>312.3</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>997.5</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>997.5</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-54.72078601345396</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>178</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>178.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>16.29</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>16.48</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>17.02</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>17.02</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>104.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>302.2</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>302.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>323.9</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>1002.62</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>1002.62</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-50.63746636127331</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>104</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>16.36</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>16.52</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>17.07</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>16.52</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>17.07</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>453.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>379.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>379.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>327.0</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>1003.74</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>1003.74</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-35.06710020239831</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>453</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>453.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>49.95</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>50.13</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>47.19</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>50.13</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>47.19</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>2760254.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>2489543.8</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>2489543.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>2608342.2</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>2056931.92</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>2056931.92</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>116547.446286709</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>2760254</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>2760254.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>49.95</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>50.11</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>47.05</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>50.11</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>47.05</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>2576995.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>2361328.0</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>2361328</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>2573029.5</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>2029667.66</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>2029667.66</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>110121.6442078613</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>2576995</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>2576995.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>50.03</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>50.11</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>46.92</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>50.11</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>46.92</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>3563323.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>2348089.0</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>2348089</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>2549300.0</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>1995061.6</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>1995061.6</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>116643.9039449403</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>3563323</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>3563323.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>50.0</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>50.08</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>46.78</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>50.08</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>46.78</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>1902947.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>2333703.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>2333703</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>2385178.1</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>1930653.14</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>1930653.14</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>16117.56414273381</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>1902947</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>1902947.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>49.8</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>50.01</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>46.64</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>50.01</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>46.64</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>1644200.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>2577326.8</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>2577326.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>2288006.9</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>1901183.2</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>1901183.2</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>49830.30856305594</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>1644200</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>1644200.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>49.74</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>49.96</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>46.51</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>49.96</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>46.51</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>2119175.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>2727140.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>2727140.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>2257097.1</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>1875176.74</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>1875176.74</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>123934.6110005495</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>2119175</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>2119175.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>49.74</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>49.92</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>46.37</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>49.92</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>46.37</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>2510800.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>2784731.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>2784731</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>2228150.6</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>1847608.44</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>1847608.44</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>174481.4855183777</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>2510800</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>2510800.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>49.57</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>49.86</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>46.23</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>49.86</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>46.23</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>3491393.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>2750511.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>2750511</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>2348177.7</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>1840232.42</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>1840232.42</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>198500.0032039052</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>3491393</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>3491393.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>49.57</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>49.8</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>46.11</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>46.11</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>3121066.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>2436653.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>2436653.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>2112008.7</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>1822330.06</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>1822330.06</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>120659.3497830899</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>3121066</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>3121066.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>49.93000000000001</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>49.75</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>46.0</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>49.75</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>46</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>2393269.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>1998687.0</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>1998687</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>2008014.5</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>1802662.46</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>1802662.46</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>44827.0466896724</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>2393269</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>2393269.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>50.29</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>49.67</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>45.89</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>49.67</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>45.89</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>2407127.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>1787053.6</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>1787053.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>1879214.6</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>1779185.08</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>1779185.08</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>12872.46917444491</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>2407127</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>2407127.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>35.61</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>36.04</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>33.85</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>36.04</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>33.85</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>10003939.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>16812721.4</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>16812721.4</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>28955598.5</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>37495260.14</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>37495260.14</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-4963789.006092828</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>10003939</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>10003939.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>35.49</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>36.15</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>33.64</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>36.15</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>33.64</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>16335914.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>24791136.2</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>24791136.2</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>29744586.4</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>37462800.8</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>37462800.8</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-4227662.37471519</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>16335914</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>16335914.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>35.94</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>36.29</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>33.43</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>36.29</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>33.43</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>11426356.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>28405642.0</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>28405642</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>30635525.9</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>37276453.84</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>37276453.84</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-3703490.852221593</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>11426356</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>11426356.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>36.5</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>36.41</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>33.23</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>36.41</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>33.23</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>23070340.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>40583749.8</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>40583749.8</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>31288459.2</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>37153017.02</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>37153017.02</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-2296382.789651394</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>23070340</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>23070340.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>36.73</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>36.54</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>33.05</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>36.54</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>33.05</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>23227058.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>39483592.2</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>39483592.2</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>32054656.6</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>36851291.98</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>36851291.98</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-1451784.457777843</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>23227058</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>23227058.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>36.55</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>36.61</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>32.83</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>36.61</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>32.83</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>49896013.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>41098475.6</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>41098475.6</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>35111442.6</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>36487231.22</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>36487231.22</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-210157.1816092804</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>49896013</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>49896013.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>36.48</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>36.7</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>32.65</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>32.65</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>34408443.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>34698036.6</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>34698036.6</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>33253068.6</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>35584667.3</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>35584667.3</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-1286286.352025293</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>34408443</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>34408443.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>35.92</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>36.71</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>32.41</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>36.71</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>32.41</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>72316895.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>32865409.8</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>32865409.8</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>37547059.9</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>35339260.36</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>35339260.36</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-1118292.440047257</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>72316895</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>72316895.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>35.37</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>36.63</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>32.15</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>36.63</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>32.15</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>17569552.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>21993168.6</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>21993168.6</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>35485008.4</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>34069635.44</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>34069635.44</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-4899981.978648372</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>17569552</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>17569552.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>35.11</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>36.68</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>31.93</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>36.68</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>31.93</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>31301475.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>24625721.0</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>24625721</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>38550535.3</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>33946568.62</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>33946568.62</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-4261609.498841092</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>31301475</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>31301475.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>35.06</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>36.67</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>31.73</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>31.73</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>17893818.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>29124409.6</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>29124409.6</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>39927956.0</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>33607601.62</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>33607601.62</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-4668725.938443527</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>17893818</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>17893818.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>40.91</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>43.42</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>46.18</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>43.42</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>46.18</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>8904509.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>14463372.6</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>14463372.6</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>14275035.1</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>15834829.58</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>15834829.58</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-659928.0818746034</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>8904509</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>8904509.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>40.86</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>43.74</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>46.32</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>43.74</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>46.32</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>11733480.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>16763563.0</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>16763563</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>14751229.7</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>16291900.36</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>16291900.36</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-199039.1212262344</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>11733480</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>11733480.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>41.18</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>44.1</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>46.5</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>46.5</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>13559467.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>17778675.4</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>17778675.4</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>15094566.9</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>16328271.62</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>16328271.62</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>163378.184029514</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>13559467</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>13559467.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>41.72000000000001</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>44.46</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>46.66</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>44.46</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>46.66</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>20113307.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>17279873.2</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>17279873.2</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>15154810.5</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>16448316.34</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>16448316.34</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>479640.7921081018</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>20113307</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>20113307.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>42.36</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>44.82</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>46.84</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>44.82</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>46.84</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>18006100.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>15689810.4</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>15689810.4</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>16170585.2</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>16258631.42</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>16258631.42</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>212117.3467879426</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>18006100</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>18006100.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>42.97</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>45.2</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>47.02</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>47.02</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>20405461.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>14086697.6</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>14086697.6</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>16201028.0</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>16174804.24</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>16174804.24</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>48137.5553738568</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>20405461</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>20405461.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>43.45</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>45.57</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>47.2</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>45.57</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>47.2</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>16809042.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>12738896.4</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>12738896.4</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>15447552.3</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>16092959.82</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>16092959.82</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-444912.8807667606</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>16809042</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>16809042.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>43.61</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>45.79</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>47.35</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>45.79</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>47.35</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>11065456.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>12410458.4</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>12410458.4</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>16703010.9</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>16066306.82</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>16066306.82</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-748050.2937974017</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>11065456</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>11065456.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>43.52</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>45.96</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>47.46</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>45.96</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>47.46</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>12162993.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>13029747.8</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>13029747.8</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>17905963.5</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>16026920.6</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>16026920.6</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-539003.4447769821</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>12162993</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>12162993.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>43.42</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>46.08</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>47.56</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>46.08</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>47.56</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>9990536.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>16651360.0</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>16651360</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>17254712.1</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>16028032.7</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>16028032.7</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-338708.2160057742</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>9990536</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>9990536.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>43.52</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>46.16</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>47.66</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>46.16</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>47.66</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>13666455.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>18315358.4</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>18315358.4</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>17040902.0</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>16015349.88</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>16015349.88</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>192287.7970961556</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>13666455</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>13666455.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
